--- a/mvp-matices/public/plantilla-matices.xlsx
+++ b/mvp-matices/public/plantilla-matices.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Inventario"/>
+    <sheet r:id="rId2" sheetId="2" name="Instrucciones"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -59,6 +60,105 @@
   </si>
   <si>
     <t>TINTE CREMA AURA 1 NEGRO 60 ML</t>
+  </si>
+  <si>
+    <t>Plantilla Matices: cómo llenarla</t>
+  </si>
+  <si>
+    <t>1. Llena la hoja Inventario: una fila por producto y por periodo. No cambies los nombres de las columnas.</t>
+  </si>
+  <si>
+    <t>2. Para varios periodos (por ejemplo julio, agosto y septiembre) agrega más filas con sus fechas, en la misma hoja.</t>
+  </si>
+  <si>
+    <t>3. Guarda como .xlsx (recomendado) o .csv y cárgalo en Matices. Deja la hoja Inventario como primera hoja.</t>
+  </si>
+  <si>
+    <t>Columna</t>
+  </si>
+  <si>
+    <t>Obligatoria</t>
+  </si>
+  <si>
+    <t>Qué poner</t>
+  </si>
+  <si>
+    <t>Ejemplo</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Primer día del periodo, AAAA-MM-DD o DD/MM/AAAA</t>
+  </si>
+  <si>
+    <t>Último día del periodo</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Código del producto en tu sistema. Si no lo tienes, déjalo vacío: el producto se identifica por su nombre</t>
+  </si>
+  <si>
+    <t>Nombre del producto, escrito igual en todos los periodos</t>
+  </si>
+  <si>
+    <t>Unidades al inicio del periodo (número entero)</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Unidades al final del periodo (número entero)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Unidades vendidas entre periodo_inicio y periodo_fin</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Unidades el día del análisis. Si no tienes la columna, bórrala: se usa el inventario final</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Unidades pedidas que aún no llegan. Vacío = 0</t>
+  </si>
+  <si>
+    <t>Costo por unidad en pesos, sin puntos de miles ni $</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>Precio de venta por unidad en pesos</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>Si tus datos vienen en archivos separados (inventario inicial, inventario final y ventas):</t>
+  </si>
+  <si>
+    <t>a. Copia la lista de productos en la columna producto.</t>
+  </si>
+  <si>
+    <t>b. Trae cada cantidad buscando por nombre, por ejemplo en inventario_final:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   =BUSCARX(D2;'[INV FINAL AGO.xlsx]Hoja1'!$A:$A;'[INV FINAL AGO.xlsx]Hoja1'!$B:$B;"NO ESTÁ")</t>
+  </si>
+  <si>
+    <t>c. Revisa que ningún producto diga NO ESTÁ y pega las columnas como valores antes de guardar.</t>
+  </si>
+  <si>
+    <t>Matices recomienda; no compra. Cada compra la decide y aprueba una persona.</t>
   </si>
 </sst>
 </file>
@@ -170,4 +270,239 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>